--- a/backend/data/all_cases.xlsx
+++ b/backend/data/all_cases.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="86">
   <si>
     <t xml:space="preserve">case_id</t>
   </si>
@@ -40,16 +40,244 @@
     <t xml:space="preserve">seq_nr_t2_sag</t>
   </si>
   <si>
+    <t xml:space="preserve">crop_x_left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crop_x_right</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pat001</t>
   </si>
   <si>
+    <t xml:space="preserve">3T</t>
+  </si>
+  <si>
     <t xml:space="preserve">25.09.2025</t>
   </si>
   <si>
+    <t xml:space="preserve">1.5T</t>
+  </si>
+  <si>
     <t xml:space="preserve">17.11.2025</t>
   </si>
   <si>
+    <t xml:space="preserve">0.55T</t>
+  </si>
+  <si>
     <t xml:space="preserve">27.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.10.2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.12.2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.06.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.06.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.02.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.06.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.07.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.02.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.04.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.04.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.07.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.06.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.07.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.10.2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09.10.2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02.10.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.03.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.04.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08.04.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.04.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.11.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03.02.2026</t>
   </si>
 </sst>
 </file>
@@ -167,8 +395,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9.2109375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H1048576"/>
+  <sheetFormatPr defaultColWidth="9.23828125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.02"/>
@@ -176,6 +404,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="27.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1021" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -198,25 +428,37 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>6</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>5</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>620</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -224,19 +466,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1.5</v>
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>4</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>240</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>660</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -244,13 +492,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.55</v>
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>5</v>
@@ -258,7 +506,1470 @@
       <c r="F4" s="0" t="n">
         <v>6</v>
       </c>
-    </row>
+      <c r="G4" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>215</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>195</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>245</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>501</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>501</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>115</v>
+      </c>
+      <c r="H28" s="0" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>270</v>
+      </c>
+      <c r="H29" s="0" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H30" s="0" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>175</v>
+      </c>
+      <c r="H31" s="0" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="H32" s="0" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H33" s="0" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="H34" s="0" t="n">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="0" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H36" s="0" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="H37" s="0" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H39" s="0" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>170</v>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="H46" s="0" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>160</v>
+      </c>
+      <c r="H47" s="0" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>155</v>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>130</v>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>155</v>
+      </c>
+      <c r="H52" s="0" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>165</v>
+      </c>
+      <c r="H53" s="0" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="H54" s="0" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="H55" s="0" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="H56" s="0" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="H57" s="0" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>145</v>
+      </c>
+      <c r="H58" s="0" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="H59" s="0" t="n">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="H60" s="0" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
